--- a/tame_output/ON/bt/strategyON_20230825.xlsx
+++ b/tame_output/ON/bt/strategyON_20230825.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>4.1%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.5%</t>
+          <t>454.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.0%</t>
         </is>
       </c>
     </row>
@@ -1375,11 +1375,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1699"/>
+  <dimension ref="A1:G1700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40587,7 +40587,7 @@
         <v>45161</v>
       </c>
       <c r="B1699" t="n">
-        <v>2.782698221366839</v>
+        <v>2.78325116388235</v>
       </c>
       <c r="C1699" t="n">
         <v>2.892305807113863</v>
@@ -40603,6 +40603,29 @@
       </c>
       <c r="G1699" t="n">
         <v>4.192699553997772</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="2" t="n">
+        <v>45162</v>
+      </c>
+      <c r="B1700" t="n">
+        <v>2.768728818568964</v>
+      </c>
+      <c r="C1700" t="n">
+        <v>2.89581178561028</v>
+      </c>
+      <c r="D1700" t="n">
+        <v>1.542452174367369</v>
+      </c>
+      <c r="E1700" t="n">
+        <v>3.512436231043481</v>
+      </c>
+      <c r="F1700" t="n">
+        <v>2.162637538641045</v>
+      </c>
+      <c r="G1700" t="n">
+        <v>4.193394308794908</v>
       </c>
     </row>
   </sheetData>
